--- a/static/reports/Kaushal Bikram Gajmer_transactions.xlsx
+++ b/static/reports/Kaushal Bikram Gajmer_transactions.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transactions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +59,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,36 +436,122 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>transaction_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45824</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>salary</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45824</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>needs</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>TransactionType</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rs 5000.00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rs 2000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Net Balance</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rs 3000.00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
